--- a/rag/esgExcelFiles/자가진단_리스크_분류_기준.xlsx
+++ b/rag/esgExcelFiles/자가진단_리스크_분류_기준.xlsx
@@ -144,7 +144,7 @@
 ② FEOC/강제노동 위반 시 즉시 고위험</t>
   </si>
   <si>
-    <t>① High 지표 50% 이상 불합격
+    <t>① High 지표 1개 이상 불합격
 ② 또는 총점 40~69점
 ③ Critical 지표는 전부 합격</t>
   </si>
@@ -262,7 +262,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -288,6 +288,9 @@
     </xf>
     <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -638,7 +641,7 @@
       <c r="B10" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="10" t="s">
         <v>35</v>
       </c>
       <c r="D10" s="8" t="s">
